--- a/www/download/COUNTRY.MLT.EXI382.xlsx
+++ b/www/download/COUNTRY.MLT.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24452331288344</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24459386503067</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.129</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.148</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.155</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.155</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.158</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.159</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.166</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.187</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.212</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.227</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.242</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.268</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.304</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.33</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.289</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.113</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.128</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.131</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.137</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.136</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.132</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.135</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.131</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.137</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.137</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.139</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.147</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.161</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.184</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.194</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.209</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.233</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.262</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.281</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>676.167</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>281.998</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>308.282</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>316.509</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>321.324</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>325.855</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>328.684</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>283.89</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>324.922</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>316.179</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>324.689</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>316.238</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>310.265</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>332.955</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>325.723</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>324.413</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>326.249</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>329.467</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>336.029</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>368.103</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>416.145</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>453.925</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>482.646</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>534.919</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>607.575</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>640.913</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>660.693</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>586.245</t>
+          <t>712255416.876192</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>211.82</t>
+          <t>441962065.846939</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>237.596</t>
+          <t>426192544.564556</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>244.487</t>
+          <t>443628365.231643</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>247.484</t>
+          <t>580261511.076118</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>250.635</t>
+          <t>763137525.071547</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>252.948</t>
+          <t>669290843.377071</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>213.68</t>
+          <t>580331524.091114</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>224.842</t>
+          <t>649325007.594537</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>221.821</t>
+          <t>661363850.598821</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>219.561</t>
+          <t>603464388.108408</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>222.454</t>
+          <t>640568680.194507</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>216.145</t>
+          <t>626980284.45388</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>232.939</t>
+          <t>624821278.315237</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>226.437</t>
+          <t>722003860.482977</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>227.403</t>
+          <t>626652943.766365</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>222.139</t>
+          <t>530361819.650759</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>233.119</t>
+          <t>558467014.163435</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>239.259</t>
+          <t>678747879.567032</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>314.033</t>
+          <t>643176930.83473</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>357.924</t>
+          <t>836903298.700707</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>384.526</t>
+          <t>606885965.750528</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>413.253</t>
+          <t>808656311.290475</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>460.535</t>
+          <t>760586124.948368</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>520.198</t>
+          <t>739744843.60048</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>545.449</t>
+          <t>772371721.598068</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>560.125</t>
+          <t>772568421.07648</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>173255313.785672</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>266494542.313819</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>167702366.600428</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>193431717.829168</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>255710530.206228</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>215746071.842264</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>248341234.383749</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>228088127.426741</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>298766900.298464</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>202317205.428719</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>227320333.181188</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>256144964.105792</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>193626442.028067</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>240690509.594076</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>383770872.791906</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>296115765.817881</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>216215040.529837</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>215382317.30849</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>201728206.258411</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>203872368.239288</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>188931407.891709</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>297723646.532263</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>355979668.354571</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>309731586.425874</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>221978149.893217</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>213359963.947995</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>291087973.115535</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3887976405.93678</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>54971461.9326298</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>238807718.192979</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>13138740.8782362</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>84548541.1590592</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>46217397.6583871</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>609070569.423154</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11297947.0595468</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>77366186.6349223</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>18195644.8712618</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>14159508.1502508</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>133935564.44585</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>23662527.9881016</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>31102859.3679305</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>15915805.9322162</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10132586.3850314</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>41134412.6025424</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10612283.5329473</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>11477893.3971155</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>19345382684.6165</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6944730.02147543</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8196880.69310461</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>9234148.8678851</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5381626.81312451</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>6811964.48471207</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>7291643.37459945</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>6103100.54666383</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1351.88229161115</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1148.36591148106</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1407.23171783502</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1485.4834727571</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1603.21121302698</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1949.43644588192</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2042.35259310154</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1598.17535475791</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1775.62826597062</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1599.04339333678</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1754.36742143967</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1852.28869292292</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1881.2318171982</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1897.56156569654</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1874.91411974969</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2115.07795823609</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2265.92350748879</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2527.24510230805</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2456.83349198589</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2940.4074263533</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>3679.10198321583</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3428.78124741186</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3995.45600338556</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>4385.54054475918</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>5517.95660620015</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>5321.27544662351</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>5443.45392343964</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2655.00517339637</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3358.50174951866</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3527.43545099793</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3774.80759494585</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5208.0181499822</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8187.56015807014</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7210.1039249097</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6060.19127724852</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6228.83295362276</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6199.90369116952</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6064.67937579158</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6886.31182522123</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6983.25132759546</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6992.69328998451</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>8097.38094764286</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>8104.72795133776</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7140.95635993232</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>8299.57326705278</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>9853.36888286294</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>9664.53017779</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>14205.7197331794</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9389.39845285816</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>13227.2645876114</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12099.7499112242</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>12538.5794769199</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12454.074627824</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>12230.2681253184</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2.38370334177301</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.205161958812137</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.416771896642983</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.263944728113028</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.0321712609940293</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.161712924179181</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0185501438277609</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.0631691249750607</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.247433367700948</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.096402056018529</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.0341339161024432</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.131530847086436</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.116298981358706</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.0322052980285117</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.409968249146472</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.232046968617418</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0273984615294895</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.0823497625666567</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.186046336492681</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.540340773009421</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.894464552991451</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.291553705874327</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.160887997502561</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.48688432533475</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.34346397875273</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.55647529112846</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.924247123310797</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>599.296548680443</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2348.7973057797</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1346.1419698219</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1512.36683212806</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1971.85788252788</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1641.52835609995</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1872.85998781128</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1660.03003949568</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2222.96800817318</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1488.72115841636</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1719.51840530409</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1895.96568546109</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1472.44442606903</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1720.44681625523</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2811.50822558168</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2159.85241296791</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1556.62376191392</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1496.74994654976</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1371.36781956788</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1265.83305811179</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1029.40184126113</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1532.59663356864</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1703.72262177571</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1330.82781859913</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>848.306640448265</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>780.323843157519</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1037.09057065053</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>23797043.5004637</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>326960220.834518</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>204759533.912844</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>287830614.68744</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>368817169.774064</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>246099359.80158</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>298926779.327427</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>338567407.922413</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>341306447.783024</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>241044319.074544</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>290309695.377592</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>302701441.473377</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>314717433.600987</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>380252191.781129</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>570428793.811414</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>542296300.885213</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>325034851.420115</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>427590659.505715</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>418829949.731857</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>480740332.764667</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>600538616.915637</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>807199263.112586</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>837932876.405263</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>713075830.695442</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>681634912.151867</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>763167516.762295</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>618124250.774629</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-67529711.7650399</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>197989732.812329</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>64896931.7452206</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>145929938.778363</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>190981748.699015</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>157705872.265513</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>171799697.633332</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>193862347.743622</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>187468230.122594</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>147082642.074438</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>178746806.977035</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>150850453.373402</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>126022776.602319</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>220656504.700308</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>295311015.878747</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>225101138.706992</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>149110948.85551</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>183755109.770936</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>115911596.819491</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>149294914.077855</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>191178262.211541</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>236842563.603216</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>202796957.640424</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>35070229.4279811</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>4366122.80187555</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>24283018.6239039</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>420440301.241258</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>91326755.2655036</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>128970488.02219</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>139862602.167623</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>141900675.909076</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>177835421.075049</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>88393487.5360667</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>127127081.694095</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>144705060.178791</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>153838217.66043</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>93961677.0001069</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>111562888.400556</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>151850988.099974</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>188694656.998668</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>159595687.080821</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>275117777.932666</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>317195162.178221</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>175923902.564606</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>243835549.734779</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>302918352.912366</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>331445418.686812</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>409360354.704096</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>570356699.50937</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>635135918.76484</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>678005601.267461</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>677268789.349991</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>738884498.138392</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>197683949.533371</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2027.84173448305</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1866.91344967326</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1907.1761117353</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1911.54808444127</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1908.42072794594</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1906.98470668792</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1907.60180995444</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1555.16739446842</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1672.93154761942</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1632.23693892599</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1660.82450832083</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1646.58771280558</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1643.68821292816</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1665.03931379552</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1658.87912087906</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1658.66520787769</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1599.2728581706</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1620.00694926979</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1626.50577838243</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1949.81427123279</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1950.16529905334</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1979.4308616961</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1977.83114269301</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1978.78702319449</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1987.97605482725</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1994.8786241106</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1995.61854718703</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2028.78165661963</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2192.48950396464</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2199.50057077626</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2198.58988608016</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2198.59048922353</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2198.60333310823</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2198.5551839464</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1836.28719275554</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2093.56958762937</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2025.49007046818</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2129.10819672138</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2033.68488745972</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2039.87508218281</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2059.0909090907</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2056.33207070735</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2039.05091137696</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2010.16019716563</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1984.74096385515</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1977.8045909363</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1969.94564453481</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1967.56884698284</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1995.97121323223</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1992.74333797349</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1992.89540722517</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1998.59229811628</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2004.16874693362</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2005.07466778877</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>895.491810925263</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3108.63726956834</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3467.32112710156</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3442.82485315513</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3850.98588988092</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4352.43854917183</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4107.5241343493</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4519.58851196395</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4290.45335544444</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3578.74318046807</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4252.42427692691</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>4963.00380903672</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5749.78653476185</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>5630.07477470898</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>7126.05887131937</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>7825.11263419727</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>6634.26653561804</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>8803.87324775228</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>9597.79619397433</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>9779.18070801536</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>12181.2578546937</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>14608.175999617</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>16215.1618459306</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17334.9776012168</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>18361.0558838442</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18810.8596848564</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>13691.9733776851</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>73641843.824752</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>155665220.15096</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>161282128.724822</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>165232331.527494</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>208526635.670274</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>349986320.739868</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>280743141.034332</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>262062178.591846</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>274125552.778412</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>263318495.039957</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>222795704.768351</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>247909370.821095</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>216610613.082251</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>244825402.456958</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>256119318.295321</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>224897515.846843</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>189146231.199186</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>228460330.266376</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>285258818.255373</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>243520582.549438</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>279831312.300161</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>270337634.87851</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>371329491.549715</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>328347131.688794</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>341032017.850107</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>347485022.3327</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>283951324.314342</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1244.22493531938</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3475.60845205782</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3679.13466779302</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3564.92857412604</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3966.68935003543</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4765.38612154107</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4206.43651322214</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4247.88036463462</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>4235.9768178647</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>3663.35311915734</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>4416.76072418813</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5201.50149850425</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>5707.06350017075</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>5649.87545306912</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7246.30189853314</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>7903.64911975376</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>6433.49364672578</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>8368.54384928962</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>8970.52675604423</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>8407.60680114165</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>10965.9593020619</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>12746.4511927329</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>13077.0882660191</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13874.273854014</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>14802.8538327059</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15333.4028881332</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>10071.3699377814</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>676.167</t>
+          <t>295005352.946488</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>281.998</t>
+          <t>557171250.968426</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>308.282</t>
+          <t>405690555.788917</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>316.509</t>
+          <t>476067082.175892</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>321.324</t>
+          <t>598568898.592022</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>325.855</t>
+          <t>660150605.759832</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>328.684</t>
+          <t>595622408.782249</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>283.89</t>
+          <t>555163697.454466</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>324.922</t>
+          <t>606177653.990824</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>316.179</t>
+          <t>519879417.372716</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>324.689</t>
+          <t>540590766.974916</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>316.238</t>
+          <t>586097288.85961</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>310.265</t>
+          <t>526022597.54077</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>332.955</t>
+          <t>627791066.319173</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>325.723</t>
+          <t>844246852.823116</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>324.413</t>
+          <t>776877523.760944</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>326.249</t>
+          <t>491028805.291527</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>329.467</t>
+          <t>608586489.329984</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>336.029</t>
+          <t>632232822.795338</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>368.103</t>
+          <t>578454252.642406</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>416.145</t>
+          <t>762893236.32676</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>453.925</t>
+          <t>880088821.916758</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>482.646</t>
+          <t>906994468.996674</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>534.919</t>
+          <t>697464633.860581</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>607.575</t>
+          <t>697919058.423513</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>640.913</t>
+          <t>773195518.947822</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>660.693</t>
+          <t>549301811.048268</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>586.245</t>
+          <t>-348.733124394121</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>211.82</t>
+          <t>-366.971182489487</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>237.596</t>
+          <t>-211.813540691466</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>244.487</t>
+          <t>-122.103720970919</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>247.484</t>
+          <t>-115.703460154511</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>250.635</t>
+          <t>-412.947572369243</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>252.948</t>
+          <t>-98.9123788728385</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>213.68</t>
+          <t>271.708147329327</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>224.842</t>
+          <t>54.4765375797346</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>221.821</t>
+          <t>-84.6099386892732</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>219.561</t>
+          <t>-164.336447261221</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>222.454</t>
+          <t>-238.497689467524</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>216.145</t>
+          <t>42.7230345910977</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>232.939</t>
+          <t>-19.800678360135</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>226.437</t>
+          <t>-120.243027213763</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>227.403</t>
+          <t>-78.5364855564962</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>222.139</t>
+          <t>200.772888892258</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>233.119</t>
+          <t>435.329398462661</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>239.259</t>
+          <t>627.269437930098</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>314.033</t>
+          <t>1371.57390687371</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>357.924</t>
+          <t>1215.29855263181</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>384.526</t>
+          <t>1861.72480688409</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>413.253</t>
+          <t>3138.07357991146</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>460.535</t>
+          <t>3460.70374720286</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>520.198</t>
+          <t>3558.20205113829</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>545.449</t>
+          <t>3477.45679672316</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>560.125</t>
+          <t>3620.60343990372</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>610.046</t>
+          <t>-221363509.121736</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>361.737</t>
+          <t>-401506030.817466</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>357.103</t>
+          <t>-244408427.064096</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>370.661</t>
+          <t>-310834750.648398</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>473.437</t>
+          <t>-390042262.921748</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>618.62</t>
+          <t>-310164285.019964</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>549.191</t>
+          <t>-314879267.747918</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>470.182</t>
+          <t>-293101518.86262</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>534.317</t>
+          <t>-332052101.212413</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>542.021</t>
+          <t>-256560922.33276</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>498.884</t>
+          <t>-317795062.206564</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>523.883</t>
+          <t>-338187918.038515</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>510.481</t>
+          <t>-309411984.458519</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>512.513</t>
+          <t>-382965663.862214</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>590.854</t>
+          <t>-588127534.527795</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>514.918</t>
+          <t>-551980007.914101</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>439.374</t>
+          <t>-301882574.09234</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>448.682</t>
+          <t>-380126159.063608</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>546.623</t>
+          <t>-346974004.539966</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>529.728</t>
+          <t>-334933670.092968</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>672.601</t>
+          <t>-483061924.026599</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>507.314</t>
+          <t>-609751187.038247</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>663.963</t>
+          <t>-535664977.446958</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>637.611</t>
+          <t>-369117502.171788</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>634.637</t>
+          <t>-356887040.573406</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>659.286</t>
+          <t>-425710496.615123</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>660.452</t>
+          <t>-265350486.733925</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>962.633299705743</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1245.31796691731</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1218.50869954703</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1312.5464199177</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1520.57742467295</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1859.98722599562</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1797.50375873891</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2095.22050806229</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2130.62374331401</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1939.90130159398</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2071.19074321945</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2219.24419534735</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2091.43081788506</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2303.66595977718</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2431.14070279847</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2500.31416107658</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2576.45987946655</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2548.14581387574</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2268.51755972247</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2366.86806546398</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1832.94212396867</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2955.87329519229</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3201.01092107104</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3577.40571624156</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3946.42741263342</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4142.79587761087</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4207.66069863299</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>362.668</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>151.119</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>170.025</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>174.579</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>178.625</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>181.701</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>189.585</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>153.043</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>185.1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>170.575</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>174.568</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>172.301</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>168.903</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>169.554</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>167.177</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>163.537</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>168.291</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>170.055</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>169.239</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>195.685</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>216.747</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>221.62</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>244.264</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>275.674</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>325.546</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>330.013</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>343.855</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1711.27844862229</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1882.61005769901</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2013.36224533431</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2167.55291997709</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2602.05430983992</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2877.4606722632</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2886.85500679897</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3140.00721140566</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3276.87771235376</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2958.34657966116</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3272.14715280943</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3488.96289505426</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3507.72862861242</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3753.63369976609</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3878.10514381948</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3956.09182069376</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4235.64650001662</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4282.5930842336</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4476.52973999133</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4555.73094056974</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4459.13237187879</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>5929.52744746062</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>5956.71451950168</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6664.22761873923</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6306.08496710146</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5634.29057278033</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7864.81126723023</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>154.186</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>227.176</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>144.658</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>167.642</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>215.094</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>183.729</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>211.518</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>192.245</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>259.454</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>173.593</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>196.03</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>218.567</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>161.67</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>202.646</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>325.879</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>251.972</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>183.524</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>179.682</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>167.3</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>171.758</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>159.159</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>255.018</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>300.751</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>265.35</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>190.783</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>182.455</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>247.2</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>280.22</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-6.76</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>64.25</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>45.84</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>36.42</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>19.59</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-13.34</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-30.52</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-9.75</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>21.04</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>29.74</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>43.01</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>82.83</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>124.88</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>73.56</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>172.66</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>198.95</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>126.59</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>4835.751</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>66.975</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>296.171</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>15.413</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>103.837</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>55.979</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>756.59</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12.49</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>95.067</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>21.328</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>16.565</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>165.564</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>28.598</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>37.721</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>18.593</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>11.634</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>50.39</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>12.347</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>13.224</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>24067.022</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>7.926</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>9.542</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>10.899</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>6.175</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>7.961</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>8.563</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>6.865</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1635.10421663825</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1591.13720660021</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1890.9280193182</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2015.67829434225</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1894.34483001052</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2284.42491295672</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2394.53940858104</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2358.96005919862</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2329.0607776194</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2734.66344481427</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2760.16057566811</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2843.73633191634</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>3313.74493019941</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>3357.87527833528</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3159.00440098708</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>3731.48023400819</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3575.85802941525</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>4057.45856759432</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>4367.17322879233</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>5251.11470061099</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>6699.76588431765</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>6033.79351535223</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>7126.48502493246</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>7651.81105706891</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>8622.46634398342</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10373.7059283489</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>8475.96233853853</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>586244584.236512</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>211819999.999972</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>237596000.000005</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>244487000.000024</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>247484000.000042</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>250635000.000048</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>252947999.999932</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>213679999.999994</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>224842000.000041</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>221820999.999971</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>219561000.000002</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>222454000.000033</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>216145000.000042</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>232938999.999965</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>226436999.999995</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>227403000.000017</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>222138999.999891</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>233118999.9999</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>239259000.000029</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>314032921.288966</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>357923855.197612</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>384526079.005162</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>413252524.347764</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>460535040.917698</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>520197798.344928</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>545449475.949108</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>560125194.897939</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>676166990.510132</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>281997999.999983</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>308282000.00002</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>316509000.000068</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>321324000.000028</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>325854999.999998</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>328683999.999948</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>283890000.00003</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>324922000.000075</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>316179000.000005</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>324688999.999989</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>316237999.999992</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>310265000.000007</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>332954999.999948</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>325723000.000043</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>324413000.000041</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>326248999.999981</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>329466999.999935</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>336029000.000037</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>368103000.349586</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>416145190.894236</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>453925476.673435</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>482645926.570051</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>534919484.901472</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>607574596.213217</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>640912695.594709</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>660693479.330843</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>362668025.971221</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>151119221.736034</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>170024845.230375</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>174579124.37185</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>178624907.643302</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>181701028.862456</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>189585046.726965</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>153043278.167387</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>185100458.765052</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>170575148.997569</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>174567886.757943</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>172300957.824652</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>168903452.638122</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>169553674.670464</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>167176923.166419</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>163536621.683301</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>168291087.922651</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>170054890.887942</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>169238617.061718</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>195684858.869986</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>216747383.718833</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>221620078.126456</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>244264465.432047</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>275673572.860224</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>325545645.275159</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>330012690.675859</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>343855143.62751</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>333287.2161496</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>128620.000000023</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>140160.000000009</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>143959.999999985</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>146150.000000004</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>148210.000000013</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>149499.999999983</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>154600.000000012</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>155199.999999998</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>156099.999999961</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>152499.99999999</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>155500.000000003</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>152100.000000001</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>161699.999999991</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>158400</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>159099.999999984</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>162300</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>165999.99999999</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>169899.999999979</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>186859.470651288</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>211502.225974137</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>227420.853399163</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>242201.751411135</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>268413.225783019</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>304001.269686604</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>319789.786451518</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>329510.661096461</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>289097.8000243</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>113460.000000023</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>124580.000000011</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>127899.999999993</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>129680.000000006</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>131430.000000029</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>132599.999999986</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>137400.000000021</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>134399.999999995</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>135899.999999957</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>132199.999999993</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>135100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>131499.999999993</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>139899.999999982</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>136500.000000002</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>137099.999999991</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>138899.999999996</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>143899.999999986</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>147099.999999983</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>161057.863778182</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>183535.136929858</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>194260.929465188</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>208942.267834392</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>232736.03248834</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>261672.064450561</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>273424.893803899</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>280677.485027124</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>676166990.510132</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>281997999.999983</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>308282000.00002</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>316509000.000068</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>321324000.000028</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>325854999.999998</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>328683999.999948</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>283890000.00003</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>324922000.000075</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>316179000.000005</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>324688999.999989</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>316237999.999992</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>310265000.000007</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>332954999.999948</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>325723000.000043</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>324413000.000041</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>326248999.999981</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>329466999.999935</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>336029000.000037</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>368103000.349586</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>416145190.894236</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>453925476.673435</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>482645926.570051</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>534919484.901472</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>607574596.213217</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>640912695.594709</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>660693479.330843</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>586244584.236512</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>211819999.999972</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>237596000.000005</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>244487000.000024</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>247484000.000042</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>250635000.000048</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>252947999.999932</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>213679999.999994</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>224842000.000041</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>221820999.999971</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>219561000.000002</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>222454000.000033</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>216145000.000042</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>232938999.999965</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>226436999.999995</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>227403000.000017</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>222138999.999891</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>233118999.9999</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>239259000.000029</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>314032921.288966</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>357923855.197612</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>384526079.005162</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>413252524.347764</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>460535040.917698</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>520197798.344928</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>545449475.949108</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>560125194.897939</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7305.23849930163</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>7927.83544558214</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>8503.60072364967</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>9005.30540205479</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>9920.83764932827</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>11656.1785183625</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>11662.5023979265</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>11310.0784042613</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>11587.8005742193</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>11363.2088777854</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>12675.3784349407</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>13549.5001613168</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>14673.6301054626</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>14888.9678113117</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16026.3517328932</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>17400.8265194214</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>16835.0166130179</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>18534.7175006438</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>19617.4576543388</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>23699.5852821213</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>27366.7472542499</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>28107.2609905556</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>31155.6962097195</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>35075.4876269131</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>37340.3460821956</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>38972.5378906953</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>37734.8104568555</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1883.06718826906</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2139.33999123148</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2252.91293464459</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2397.64164934066</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2885.94406109832</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3177.47646543012</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3256.47261173509</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3520.27843847743</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3629.65962586812</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>3312.91858721643</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>3635.74884979753</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>3879.83513922131</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3888.34084900133</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4240.04569735125</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4450.73477695582</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>4474.24722130261</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>4926.75673264062</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>4867.93546020936</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>5153.64668409884</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>5346.97008130272</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>5315.92943592823</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>6864.454530293</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>6962.37766822525</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>7784.56955960972</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>7903.49684770474</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>6864.39890742375</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>9412.80314282596</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
